--- a/samples/기준표_기본값.xlsx
+++ b/samples/기준표_기본값.xlsx
@@ -502,7 +502,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5. 점검코드는 도구에 들어 있는 규칙 이름입니다. 없는 이름을 적으면 넣을 때 알려 줍니다: CAPTIONS, CITATION_LIST, CITATION_REF, EQUATIONS, EXISTS, FIX_TEMPLATE, FLOWCHART, PURPOSE, QUANT, SECTION_JUDGE, SECTION_SEQUENCE, TEMPLATE_ITEMS, TERM_CONSISTENCY, TERM_DEF</t>
+          <t>5. 점검코드는 도구에 들어 있는 규칙 이름입니다. 없는 이름을 적으면 넣을 때 알려 줍니다: CAPTIONS, CITATION_LIST, CITATION_REF, EQUATIONS, EXISTS, FIX_TEMPLATE, FLOWCHART, LEFTOVER, PURPOSE, QUANT, REVISION, SECTION_JUDGE, SECTION_SEQUENCE, TEMPLATE_ITEMS, TERM_CONSISTENCY, TERM_DEF</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -671,34 +671,30 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>공통-3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1항 목적 및 정의</t>
+          <t>전체(머리글·개정 이력)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>작성된 표준의 목적과 정의를 구체적으로 정리하여, 제목의 내용에 대한 표준 문서의 목적과 정의를 구체적으로 정리해야 함</t>
+          <t>(Template 학습에서 추가, 가정) 머리글의 표준번호·날짜·Rev 와 개정 이력이 Template 형식대로 채워지고 서로 맞아야 함</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>판단(프롬프트) + 보조</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>PURPOSE</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>REVISION</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -709,27 +705,27 @@
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1항의 목적과 정의가 표준 제목의 내용에 맞게 구체적으로 적혀 있는지 판단해 주세요. 막연한 표현(예: 품질 향상을 위해)만 있는 문장은 지적해 주세요.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Template 을 학습하면 개정 이력 칸이 필수인지 Template 에서 알아냅니다. 학습 전에는 설정 「개정이력_필수」를 따릅니다.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>공통-4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2항 관련 표준 및 인용</t>
+          <t>전체(작성 완결성)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>표준의 내용에 관련된 표준과 검토된 기술지식에 대한 문서번호와 제목이 정리되어야 함</t>
+          <t>(Template 학습에서 추가, 가정) Template 의 예시 문구·자리표시(xx, 0000)와 「추후 보완 예정」 같은 미완성 표기가 남아 있지 않아야 함</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -739,14 +735,10 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>CITATION_LIST</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>LEFTOVER</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -758,37 +750,41 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>예시 문구 대조는 Template 을 학습한 뒤부터 됩니다. 미완성 표기는 학습 없이도 찾습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3항 용어정의</t>
+          <t>1항 목적 및 정의</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>표준에 사용된 용어에 대한 정의로, 일반적인 상식이 아닌 작성된 표준에 적용되는 용어에 대한 정리와 설명이 구체적으로 정리되어야 함</t>
+          <t>작성된 표준의 목적과 정의를 구체적으로 정리하여, 제목의 내용에 대한 표준 문서의 목적과 정의를 구체적으로 정리해야 함</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>보조 + 판단(프롬프트)</t>
+          <t>판단(프롬프트) + 보조</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>TERM_DEF</t>
+          <t>PURPOSE</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -803,7 +799,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>용어정의의 각 설명이 일반 상식 수준의 사전 뜻인지, 이 표준에 적용되는 뜻으로 구체적으로 적혀 있는지 용어별로 판단해 주세요.</t>
+          <t>1항의 목적과 정의가 표준 제목의 내용에 맞게 구체적으로 적혀 있는지 판단해 주세요. 막연한 표현(예: 품질 향상을 위해)만 있는 문장은 지적해 주세요.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -811,17 +807,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3항 용어정의 ↔ 본문 전체</t>
+          <t>2항 관련 표준 및 인용</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>정리된 용어정의는 표준 전체에 동일 기준으로 사용되어야 함. 용어가 통일되게 사용되지 않은 것도 지적 대상 (예: ECU는 계속 ECU로 써야 하며, 한글 「이씨유」 표기 불가)</t>
+          <t>표준의 내용에 관련된 표준과 검토된 기술지식에 대한 문서번호와 제목이 정리되어야 함</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -831,10 +827,14 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>TERM_CONSISTENCY</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
+          <t>CITATION_LIST</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -846,41 +846,37 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>원문 예시의 「EUC」는 ECU 의 오기로 보았습니다(가정).</t>
-        </is>
-      </c>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4항 설계절차/시험절차</t>
+          <t>3항 용어정의</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>설계절차/시험절차는 설계 방법을 항목 순서 기준으로 정리함</t>
+          <t>표준에 사용된 용어에 대한 정의로, 일반적인 상식이 아닌 작성된 표준에 적용되는 용어에 대한 정리와 설명이 구체적으로 정리되어야 함</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>자동 + 보조</t>
+          <t>보조 + 판단(프롬프트)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>SECTION_SEQUENCE</t>
+          <t>TERM_DEF</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -893,40 +889,40 @@
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>용어정의의 각 설명이 일반 상식 수준의 사전 뜻인지, 이 표준에 적용되는 뜻으로 구체적으로 적혀 있는지 용어별로 판단해 주세요.</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4항 설계절차/시험절차</t>
+          <t>3항 용어정의 ↔ 본문 전체</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4.1 또는 4.2항에 설계절차, 시험절차를 ISO 기준으로 FlowChart로 제시해야 함</t>
+          <t>정리된 용어정의는 표준 전체에 동일 기준으로 사용되어야 함. 용어가 통일되게 사용되지 않은 것도 지적 대상 (예: ECU는 계속 ECU로 써야 하며, 한글 「이씨유」 표기 불가)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>자동 + 보조</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>FLOWCHART</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>TERM_CONSISTENCY</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -940,34 +936,34 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>ISO 기호 준수 여부는 그림 판독이 필요해 검토자 확인 항목입니다.</t>
+          <t>원문 예시의 「EUC」는 ECU 의 오기로 보았습니다(가정).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4항 이하</t>
+          <t>4항 설계절차/시험절차</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>설계·시험 관련 절차를 정리하며 가능하면 수식으로 제시해야 함</t>
+          <t>설계절차/시험절차는 설계 방법을 항목 순서 기준으로 정리함</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>보조</t>
+          <t>자동 + 보조</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>EQUATIONS</t>
+          <t>SECTION_SEQUENCE</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,39 +982,39 @@
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>「가능하면」이므로 부적합이 아니라 권고로 적습니다.</t>
-        </is>
-      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>4항 이하</t>
+          <t>4항 설계절차/시험절차</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>작성되는 내용 중 그림, 표에는 반드시 표1, 그림(Fig)1 등 번호가 기재되어야 함</t>
+          <t>4.1 또는 4.2항에 설계절차, 시험절차를 ISO 기준으로 FlowChart로 제시해야 함</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>자동</t>
+          <t>자동 + 보조</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>CAPTIONS</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
+          <t>FLOWCHART</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1030,33 +1026,41 @@
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>ISO 기호 준수 여부는 그림 판독이 필요해 검토자 확인 항목입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1항 ↔ 4항 이하</t>
+          <t>4항 이하</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1항 목적 및 범위에 정리된 내용과 4항 이하 설계·시험절차에 정리된 내용을 비교하여 논리적으로 MECE 해야 함</t>
+          <t>설계·시험 관련 절차를 정리하며 가능하면 수식으로 제시해야 함</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>판단(프롬프트)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>보조</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>EQUATIONS</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,4+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1069,17 +1073,17 @@
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1항에 적힌 목적·범위의 요소를 목록으로 뽑은 뒤, 4항 이하 절차가 그 요소를 빠짐없이(누락 없음) 다루는지, 서로 겹치지 않는지(중복 없음) 판단해 주세요. 누락과 중복을 나눠 적어 주세요.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>「가능하면」이므로 부적합이 아니라 권고로 적습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1089,24 +1093,20 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>구체적 기준에 대해 근거를 명확하게 정량화하여 표현하고, 관련된 표준·법규 등은 반드시 근거를 명확히 제시해야 함. 제시된 표준 No.와 제목이 맞는지 확인 필요</t>
+          <t>작성되는 내용 중 그림, 표에는 반드시 표1, 그림(Fig)1 등 번호가 기재되어야 함</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>자동 + 보조 + 판단</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CITATION_REF</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4+</t>
-        </is>
-      </c>
+          <t>CAPTIONS</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1117,31 +1117,23 @@
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4항 이하의 기준 문장이 수치와 단위로 정량화되어 있는지, 수치 기준마다 근거(표준·법규·시험 결과)가 제시되어 있는지 판단해 주세요.</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>원문의 「정수화」는 「정량화」로 보았습니다(가정). 사내 표준 목록과의 번호-제목 대조는 목록 확보 후(확장).</t>
-        </is>
-      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>4항</t>
+          <t>1항 ↔ 4항 이하</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>(원문 「7)」 이후 내용 없음 — 기준 확인 필요)</t>
+          <t>1항 목적 및 범위에 정리된 내용과 4항 이하 설계·시험절차에 정리된 내용을 비교하여 논리적으로 MECE 해야 함</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1152,12 +1144,12 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>1,4+</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1165,42 +1157,42 @@
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>기준을 채운 뒤 사용을 Y 로 바꾸면 판단 프롬프트가 만들어집니다.</t>
-        </is>
-      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1항에 적힌 목적·범위의 요소를 목록으로 뽑은 뒤, 4항 이하 절차가 그 요소를 빠짐없이(누락 없음) 다루는지, 서로 겹치지 않는지(중복 없음) 판단해 주세요. 누락과 중복을 나눠 적어 주세요.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>5항 설계/시험 검증</t>
+          <t>4항 이하</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>설계 또는 시험 방법에 제시한 사항을 검증하는 방법을 제시해야 함</t>
+          <t>구체적 기준에 대해 근거를 명확하게 정량화하여 표현하고, 관련된 표준·법규 등은 반드시 근거를 명확히 제시해야 함. 제시된 표준 No.와 제목이 맞는지 확인 필요</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>보조 + 판단(프롬프트)</t>
+          <t>자동 + 보조 + 판단</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SECTION_JUDGE</t>
+          <t>CITATION_REF</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4+,5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1215,45 +1207,45 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4항 이하의 절차마다 5항에 대응하는 검증 방법이 있는지 절차별로 짝지어 판단해 주세요. 검증 방법이 없는 절차를 적어 주세요.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
+          <t>4항 이하의 기준 문장이 수치와 단위로 정량화되어 있는지, 수치 기준마다 근거(표준·법규·시험 결과)가 제시되어 있는지 판단해 주세요.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>원문의 「정수화」는 「정량화」로 보았습니다(가정). 사내 표준 목록과의 번호-제목 대조는 목록 확보 후(확장).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>5항 설계/시험 검증</t>
+          <t>4항</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>최대한 정성적이 아닌 정량적 기준으로 관련 근거를 제기해야 함</t>
+          <t>(원문 「7)」 이후 내용 없음 — 기준 확인 필요)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>보조 + 판단(프롬프트)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>QUANT</t>
-        </is>
-      </c>
+          <t>판단(프롬프트)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1261,43 +1253,47 @@
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5항의 검증 기준이 정량적(수치·단위·허용 범위)인지 판단해 주세요. 정성 표현만 있는 문장은 정량 기준으로 바꾸는 예를 들어 주세요.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>기준을 채운 뒤 사용을 Y 로 바꾸면 판단 프롬프트가 만들어집니다.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>5항</t>
+          <t>5항 설계/시험 검증</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>(원문 「3)」 이후 내용 없음 — 기준 확인 필요)</t>
+          <t>설계 또는 시험 방법에 제시한 사항을 검증하는 방법을 제시해야 함</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>판단(프롬프트)</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>보조 + 판단(프롬프트)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>SECTION_JUDGE</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1305,42 +1301,42 @@
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>기준을 채운 뒤 사용을 Y 로 바꾸면 판단 프롬프트가 만들어집니다.</t>
-        </is>
-      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4항 이하의 절차마다 5항에 대응하는 검증 방법이 있는지 절차별로 짝지어 판단해 주세요. 검증 방법이 없는 절차를 적어 주세요.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>6항</t>
+          <t>5항 설계/시험 검증</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>(원문에 항목명과 기준 「1)」 모두 비어 있음) — 항목명이 정해지기 전까지 존재 여부만 점검</t>
+          <t>최대한 정성적이 아닌 정량적 기준으로 관련 근거를 제기해야 함</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>자동(존재만)</t>
+          <t>보조 + 판단(프롬프트)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>EXISTS</t>
+          <t>QUANT</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1353,43 +1349,43 @@
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5항의 검증 기준이 정량적(수치·단위·허용 범위)인지 판단해 주세요. 정성 표현만 있는 문장은 정량 기준으로 바꾸는 예를 들어 주세요.</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>7항 안전 관련 사항</t>
+          <t>5항</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>표준을 설계/시험하며 지켜져야 할 안전 기준에 대해 정리되어야 함</t>
+          <t>(원문 「3)」 이후 내용 없음 — 기준 확인 필요)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>보조 + 판단(프롬프트)</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>SECTION_JUDGE</t>
-        </is>
-      </c>
+          <t>판단(프롬프트)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1397,56 +1393,148 @@
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7항에 설계·시험 중 지켜야 할 안전 기준이 구체적으로(대상, 조건, 한계값, 조치) 정리되어 있는지 판단해 주세요.</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>기준을 채운 뒤 사용을 Y 로 바꾸면 판단 프롬프트가 만들어집니다.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>6항</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>(원문에 항목명과 기준 「1)」 모두 비어 있음) — 항목명이 정해지기 전까지 존재 여부만 점검</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>자동(존재만)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>EXISTS</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Template {항목} 기준에 따라 {내용}</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>7-1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>7항 안전 관련 사항</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>표준을 설계/시험하며 지켜져야 할 안전 기준에 대해 정리되어야 함</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>보조 + 판단(프롬프트)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>SECTION_JUDGE</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Template {항목} 기준에 따라 {내용}</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>7항에 설계·시험 중 지켜야 할 안전 기준이 구체적으로(대상, 조건, 한계값, 조치) 정리되어 있는지 판단해 주세요.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>8-1</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>8항 기타(Appendix)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>표준 내용을 보완하여 설명을 추가</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>자동(존재만)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>EXISTS</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Template {항목} 기준에 따라 {내용}</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>필수인지 선택인지 확인 필요 — 항목 시트의 필수 값을 따릅니다(기본 N, 가정).</t>
         </is>
@@ -2228,7 +2316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2298,10 +2386,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>법령 공포번호(…령 제 n호)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>제\s?\d{1,5}\s?호</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>사내 표준(예시 형식, 가정 — 실제 규칙으로 교체)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>\b[A-Z]{2,5}-\d{3,6}(?:-\d+)?\b</t>
         </is>
@@ -2318,7 +2418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2499,15 +2599,32 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>개정이력_필수</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>예: 개정 이력이 없으면 부적합. Template 을 학습하면 Template 에 개정 이력이 있는지로 정합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>수치_단위_정규식</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>\d+(?:\.\d+)?\s?(?:%|℃|°C|mm|cm|km|m|kg|g|kN|N·m|Nm|N|MPa|kPa|Pa|bar|mV|V|mA|A|kW|W|kHz|Hz|rpm|ms|s|min|h|dB|mL|L|시간|분|초|회|개|배)(?![A-Za-z가-힣])</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>수치+단위 문장을 찾는 정규식. 사내에서 쓰는 단위를 더합니다.</t>
         </is>
